--- a/analysis/app_responses.xlsx
+++ b/analysis/app_responses.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
@@ -42,7 +42,17 @@
     <x:t xml:space="preserve">Name</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Last modified time</x:t>
+    <x:t xml:space="preserve">Gender</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Age Group</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">In a typical week, about how many days do you spend at least 30 minutes playing a video game?
+</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Are You familiar with Game Design concepts?</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">This is a sample map from the game Dragon Warrior.
@@ -55,58 +65,91 @@
 Local Pattern: A pattern that can be identified...</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">How difficult it was to guide the algorithm to realize your design ideas (1-Very Difficult, 5-Not difficult at all)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Does the Map have Local Patterns (1- No Local Patterns, 5 - Many Local Patterns)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Does the Map have a  Global Pattern (1- No Global Pattern, 5 - Clear Global Pattern)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">How much does the game maps generated look like they could be from the Dragon Warrior? (1- Not at all, 5 - It could be a part of Dragon Warrior)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">How difficult it was to guide the algorithm to realize your design ideas (1-Very Difficult, 5-Not difficult at all)2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Does the Map have Local Patterns (1- No Local Patterns, 5 - Many Local Patterns)2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Does the Map have a  Global Pattern (1- No Global Pattern, 5 - Clear Global Patterns)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">How much does the game maps generated look like they could be from the Dragon Warrior? (1- Not at all, 5 - It could be a part of Dragon Warrior)2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">How difficult it was to guide the algorithm to realize your design ideas (1-Very Difficult, 5-Not difficult at all)3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Does the Map have Local Patterns (1- No Local Patterns, 5 - Many Local Patterns)3</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Does the Map have a  Global Pattern (1- No Global Pattern, 5 - Clear Global Patterns)2</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">How much does the game maps generated look like they could be from the Dragon Warrior? (1- Not at all, 5 - It could be a part of Dragon Warrior)3</x:t>
+    <x:t xml:space="preserve">It was easy to guide the algorithm to realize my design ideas </x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Map has Many Local Patterns</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Map has a Global Pattern</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Generated Game Maps look like they could be from the game Dragon Warrior</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">It was easy to guide the algorithm to realize my design ideas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Map has Many Local Patterns2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Map has a Global Pattern2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Generated Game Maps look like they could be from the game Dragon Warrior2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">It was easy to guide the algorithm to realize my design ideas2</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Map has Many Local Patterns3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Map has a Global Pattern3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">The Generated Game Maps look like they could be from the game Dragon Warrior3</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">anonymous</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">Male</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">18-25</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">6-7</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Yes</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">3</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">4</x:t>
   </x:si>
   <x:si>
+    <x:t xml:space="preserve">5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">1</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">2</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">5</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1</x:t>
+    <x:t xml:space="preserve">Female</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">No</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">26-35</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0-1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">4-5</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">2-3</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Non-binary</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -203,29 +246,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T15" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:T15"/>
-  <x:tableColumns count="20">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:W21" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:W21"/>
+  <x:tableColumns count="23">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
     <x:tableColumn id="3" uniqueName="3" name="Completion time" dataDxfId="3"/>
     <x:tableColumn id="4" uniqueName="4" name="Email" dataDxfId="0"/>
     <x:tableColumn id="5" uniqueName="5" name="Name" dataDxfId="0"/>
-    <x:tableColumn id="6" uniqueName="6" name="Last modified time" dataDxfId="3"/>
-    <x:tableColumn id="7" uniqueName="7" name="This is a sample map from the game Dragon Warrior.&#10;&#10;Please take a good look at it, it is referenced in future questions.&#10;&#10;(You can scroll back here if you need to)." dataDxfId="0"/>
-    <x:tableColumn id="8" uniqueName="8" name="Recognizing Local and Global Patterns:&#10;The goal of our PCG Algorithm is to create maps with Local and Global Patterns. These are defined as follows:&#10;Local Pattern: A pattern that can be identified..." dataDxfId="0"/>
-    <x:tableColumn id="9" uniqueName="9" name="How difficult it was to guide the algorithm to realize your design ideas (1-Very Difficult, 5-Not difficult at all)" dataDxfId="0"/>
-    <x:tableColumn id="10" uniqueName="10" name="Does the Map have Local Patterns (1- No Local Patterns, 5 - Many Local Patterns)" dataDxfId="0"/>
-    <x:tableColumn id="11" uniqueName="11" name="Does the Map have a  Global Pattern (1- No Global Pattern, 5 - Clear Global Pattern)" dataDxfId="0"/>
-    <x:tableColumn id="12" uniqueName="12" name="How much does the game maps generated look like they could be from the Dragon Warrior? (1- Not at all, 5 - It could be a part of Dragon Warrior)" dataDxfId="0"/>
-    <x:tableColumn id="13" uniqueName="13" name="How difficult it was to guide the algorithm to realize your design ideas (1-Very Difficult, 5-Not difficult at all)2" dataDxfId="0"/>
-    <x:tableColumn id="14" uniqueName="14" name="Does the Map have Local Patterns (1- No Local Patterns, 5 - Many Local Patterns)2" dataDxfId="0"/>
-    <x:tableColumn id="15" uniqueName="15" name="Does the Map have a  Global Pattern (1- No Global Pattern, 5 - Clear Global Patterns)" dataDxfId="0"/>
-    <x:tableColumn id="16" uniqueName="16" name="How much does the game maps generated look like they could be from the Dragon Warrior? (1- Not at all, 5 - It could be a part of Dragon Warrior)2" dataDxfId="0"/>
-    <x:tableColumn id="17" uniqueName="17" name="How difficult it was to guide the algorithm to realize your design ideas (1-Very Difficult, 5-Not difficult at all)3" dataDxfId="0"/>
-    <x:tableColumn id="18" uniqueName="18" name="Does the Map have Local Patterns (1- No Local Patterns, 5 - Many Local Patterns)3" dataDxfId="0"/>
-    <x:tableColumn id="19" uniqueName="19" name="Does the Map have a  Global Pattern (1- No Global Pattern, 5 - Clear Global Patterns)2" dataDxfId="0"/>
-    <x:tableColumn id="20" uniqueName="20" name="How much does the game maps generated look like they could be from the Dragon Warrior? (1- Not at all, 5 - It could be a part of Dragon Warrior)3" dataDxfId="0"/>
+    <x:tableColumn id="6" uniqueName="6" name="Gender" dataDxfId="0"/>
+    <x:tableColumn id="7" uniqueName="7" name="Age Group" dataDxfId="0"/>
+    <x:tableColumn id="8" uniqueName="8" name="In a typical week, about how many days do you spend at least 30 minutes playing a video game?&#10;" dataDxfId="0"/>
+    <x:tableColumn id="9" uniqueName="9" name="Are You familiar with Game Design concepts?" dataDxfId="0"/>
+    <x:tableColumn id="10" uniqueName="10" name="This is a sample map from the game Dragon Warrior.&#10;&#10;Please take a good look at it, it is referenced in future questions.&#10;&#10;(You can scroll back here if you need to)." dataDxfId="0"/>
+    <x:tableColumn id="11" uniqueName="11" name="Recognizing Local and Global Patterns:&#10;The goal of our PCG Algorithm is to create maps with Local and Global Patterns. These are defined as follows:&#10;Local Pattern: A pattern that can be identified..." dataDxfId="0"/>
+    <x:tableColumn id="12" uniqueName="12" name="It was easy to guide the algorithm to realize my design ideas " dataDxfId="0"/>
+    <x:tableColumn id="13" uniqueName="13" name="The Map has Many Local Patterns" dataDxfId="0"/>
+    <x:tableColumn id="14" uniqueName="14" name="The Map has a Global Pattern" dataDxfId="0"/>
+    <x:tableColumn id="15" uniqueName="15" name="The Generated Game Maps look like they could be from the game Dragon Warrior" dataDxfId="0"/>
+    <x:tableColumn id="16" uniqueName="16" name="It was easy to guide the algorithm to realize my design ideas" dataDxfId="0"/>
+    <x:tableColumn id="17" uniqueName="17" name="The Map has Many Local Patterns2" dataDxfId="0"/>
+    <x:tableColumn id="18" uniqueName="18" name="The Map has a Global Pattern2" dataDxfId="0"/>
+    <x:tableColumn id="19" uniqueName="19" name="The Generated Game Maps look like they could be from the game Dragon Warrior2" dataDxfId="0"/>
+    <x:tableColumn id="20" uniqueName="20" name="It was easy to guide the algorithm to realize my design ideas2" dataDxfId="0"/>
+    <x:tableColumn id="21" uniqueName="21" name="The Map has Many Local Patterns3" dataDxfId="0"/>
+    <x:tableColumn id="22" uniqueName="22" name="The Map has a Global Pattern3" dataDxfId="0"/>
+    <x:tableColumn id="23" uniqueName="23" name="The Generated Game Maps look like they could be from the game Dragon Warrior3" dataDxfId="0"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -551,6 +597,9 @@
     <x:col min="18" max="18" width="20" hidden="0" bestFit="1" customWidth="1"/>
     <x:col min="19" max="19" width="20" hidden="0" bestFit="1" customWidth="1"/>
     <x:col min="20" max="20" width="20" hidden="0" bestFit="1" customWidth="1"/>
+    <x:col min="21" max="21" width="20" hidden="0" bestFit="1" customWidth="1"/>
+    <x:col min="22" max="22" width="20" hidden="0" bestFit="1" customWidth="1"/>
+    <x:col min="23" max="23" width="20" hidden="0" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" hidden="0">
@@ -614,768 +663,1321 @@
       <x:c r="T1" s="10" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="U1" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="V1" s="10" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="W1" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" hidden="0">
       <x:c r="A2">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="2">
-        <x:v>45685.7007407407</x:v>
+        <x:v>45751.6787615741</x:v>
       </x:c>
       <x:c r="C2" s="2">
-        <x:v>45685.7133912037</x:v>
+        <x:v>45751.6871527778</x:v>
       </x:c>
       <x:c r="D2" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="10" t="s"/>
-      <x:c r="F2" s="2"/>
-      <x:c r="G2" s="10" t="s"/>
-      <x:c r="H2" s="10" t="s"/>
-      <x:c r="I2" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J2" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K2" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="F2" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G2" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H2" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I2" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J2" s="10" t="s"/>
+      <x:c r="K2" s="10" t="s"/>
       <x:c r="L2" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M2" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="N2" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O2" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P2" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q2" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R2" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S2" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="T2" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="U2" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V2" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="W2" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="3" hidden="0">
       <x:c r="A3">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="2">
-        <x:v>45685.7352199074</x:v>
+        <x:v>45751.9054976852</x:v>
       </x:c>
       <x:c r="C3" s="2">
-        <x:v>45685.7444560185</x:v>
+        <x:v>45751.9084027778</x:v>
       </x:c>
       <x:c r="D3" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E3" s="10" t="s"/>
-      <x:c r="F3" s="2"/>
-      <x:c r="G3" s="10" t="s"/>
-      <x:c r="H3" s="10" t="s"/>
-      <x:c r="I3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K3" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="F3" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G3" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I3" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="s"/>
+      <x:c r="K3" s="10" t="s"/>
       <x:c r="L3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="M3" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N3" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P3" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R3" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S3" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="T3" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="V3" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W3" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="4" hidden="0">
       <x:c r="A4">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="2">
-        <x:v>45685.7470486111</x:v>
+        <x:v>45751.9863310185</x:v>
       </x:c>
       <x:c r="C4" s="2">
-        <x:v>45685.7569444444</x:v>
+        <x:v>45751.9928819444</x:v>
       </x:c>
       <x:c r="D4" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E4" s="10" t="s"/>
-      <x:c r="F4" s="2"/>
-      <x:c r="G4" s="10" t="s"/>
-      <x:c r="H4" s="10" t="s"/>
-      <x:c r="I4" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J4" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K4" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="F4" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G4" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H4" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I4" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J4" s="10" t="s"/>
+      <x:c r="K4" s="10" t="s"/>
       <x:c r="L4" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="M4" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N4" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O4" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P4" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="Q4" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R4" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="S4" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T4" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="U4" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="V4" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="W4" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="5" hidden="0">
       <x:c r="A5">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="2">
-        <x:v>45685.7645717593</x:v>
+        <x:v>45752.6562037037</x:v>
       </x:c>
       <x:c r="C5" s="2">
-        <x:v>45685.769837963</x:v>
+        <x:v>45752.6644675926</x:v>
       </x:c>
       <x:c r="D5" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E5" s="10" t="s"/>
-      <x:c r="F5" s="2"/>
-      <x:c r="G5" s="10" t="s"/>
-      <x:c r="H5" s="10" t="s"/>
-      <x:c r="I5" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="J5" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="K5" s="7" t="s">
-        <x:v>25</x:v>
-      </x:c>
+      <x:c r="F5" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G5" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H5" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I5" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J5" s="10" t="s"/>
+      <x:c r="K5" s="10" t="s"/>
       <x:c r="L5" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M5" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N5" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O5" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P5" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="Q5" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R5" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S5" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="T5" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="U5" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="V5" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W5" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" hidden="0">
       <x:c r="A6">
-        <x:v>5</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="2">
-        <x:v>45685.7744791667</x:v>
+        <x:v>45753.9408449074</x:v>
       </x:c>
       <x:c r="C6" s="2">
-        <x:v>45685.7933564815</x:v>
+        <x:v>45753.945775463</x:v>
       </x:c>
       <x:c r="D6" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E6" s="10" t="s"/>
-      <x:c r="F6" s="2"/>
-      <x:c r="G6" s="10" t="s"/>
-      <x:c r="H6" s="10" t="s"/>
-      <x:c r="I6" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J6" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K6" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
+      <x:c r="F6" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G6" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H6" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I6" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J6" s="10" t="s"/>
+      <x:c r="K6" s="10" t="s"/>
       <x:c r="L6" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M6" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N6" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O6" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="P6" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="Q6" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R6" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S6" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T6" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U6" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="V6" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W6" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" hidden="0">
       <x:c r="A7">
-        <x:v>6</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="2">
-        <x:v>45685.8877314815</x:v>
+        <x:v>45753.9408449074</x:v>
       </x:c>
       <x:c r="C7" s="2">
-        <x:v>45685.8948611111</x:v>
+        <x:v>45753.9499652778</x:v>
       </x:c>
       <x:c r="D7" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="10" t="s"/>
-      <x:c r="F7" s="2"/>
-      <x:c r="G7" s="10" t="s"/>
-      <x:c r="H7" s="10" t="s"/>
-      <x:c r="I7" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J7" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K7" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
+      <x:c r="F7" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G7" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H7" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I7" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J7" s="10" t="s"/>
+      <x:c r="K7" s="10" t="s"/>
       <x:c r="L7" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M7" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N7" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O7" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P7" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="Q7" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R7" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="S7" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T7" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="U7" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="V7" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W7" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" hidden="0">
       <x:c r="A8">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="2">
-        <x:v>45685.900625</x:v>
+        <x:v>45753.9416087963</x:v>
       </x:c>
       <x:c r="C8" s="2">
-        <x:v>45685.9010300926</x:v>
+        <x:v>45753.9875115741</x:v>
       </x:c>
       <x:c r="D8" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E8" s="10" t="s"/>
-      <x:c r="F8" s="2"/>
-      <x:c r="G8" s="10" t="s"/>
-      <x:c r="H8" s="10" t="s"/>
-      <x:c r="I8" s="7" t="s">
+      <x:c r="F8" s="10" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J8" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="K8" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
+      <x:c r="G8" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H8" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I8" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J8" s="10" t="s"/>
+      <x:c r="K8" s="10" t="s"/>
       <x:c r="L8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="M8" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O8" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P8" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T8" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U8" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V8" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W8" s="7" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="9" hidden="0">
       <x:c r="A9">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="2">
-        <x:v>45685.8985185185</x:v>
+        <x:v>45754.3827893518</x:v>
       </x:c>
       <x:c r="C9" s="2">
-        <x:v>45685.9036921296</x:v>
+        <x:v>45754.3938078704</x:v>
       </x:c>
       <x:c r="D9" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E9" s="10" t="s"/>
-      <x:c r="F9" s="2"/>
-      <x:c r="G9" s="10" t="s"/>
-      <x:c r="H9" s="10" t="s"/>
-      <x:c r="I9" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J9" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="K9" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="F9" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G9" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H9" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I9" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J9" s="10" t="s"/>
+      <x:c r="K9" s="10" t="s"/>
       <x:c r="L9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="M9" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N9" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O9" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="P9" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="R9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="T9" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="U9" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="V9" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W9" s="7" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="10" hidden="0">
       <x:c r="A10">
-        <x:v>9</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="2">
-        <x:v>45685.9441087963</x:v>
+        <x:v>45754.4585069444</x:v>
       </x:c>
       <x:c r="C10" s="2">
-        <x:v>45685.9662152778</x:v>
+        <x:v>45754.4672916667</x:v>
       </x:c>
       <x:c r="D10" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E10" s="10" t="s"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="10" t="s"/>
-      <x:c r="H10" s="10" t="s"/>
-      <x:c r="I10" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J10" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K10" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
+      <x:c r="F10" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G10" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H10" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I10" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J10" s="10" t="s"/>
+      <x:c r="K10" s="10" t="s"/>
       <x:c r="L10" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M10" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N10" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="O10" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="P10" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="R10" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="S10" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="T10" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="U10" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="V10" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W10" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="11" hidden="0">
       <x:c r="A11">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="2">
-        <x:v>45685.9737268519</x:v>
+        <x:v>45754.458125</x:v>
       </x:c>
       <x:c r="C11" s="2">
-        <x:v>45685.9881018518</x:v>
+        <x:v>45754.4698611111</x:v>
       </x:c>
       <x:c r="D11" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E11" s="10" t="s"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="10" t="s"/>
-      <x:c r="H11" s="10" t="s"/>
-      <x:c r="I11" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J11" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K11" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="F11" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G11" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H11" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I11" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J11" s="10" t="s"/>
+      <x:c r="K11" s="10" t="s"/>
       <x:c r="L11" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M11" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="N11" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="O11" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P11" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="Q11" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R11" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="S11" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="T11" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U11" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V11" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="W11" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="12" hidden="0">
       <x:c r="A12">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="2">
-        <x:v>45685.9824421296</x:v>
+        <x:v>45754.4617592593</x:v>
       </x:c>
       <x:c r="C12" s="2">
-        <x:v>45685.9901851852</x:v>
+        <x:v>45754.4753356481</x:v>
       </x:c>
       <x:c r="D12" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E12" s="10" t="s"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="10" t="s"/>
-      <x:c r="H12" s="10" t="s"/>
-      <x:c r="I12" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J12" s="7" t="s">
+      <x:c r="F12" s="10" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="K12" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="G12" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H12" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I12" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J12" s="10" t="s"/>
+      <x:c r="K12" s="10" t="s"/>
       <x:c r="L12" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="M12" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="N12" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O12" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="P12" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R12" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S12" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T12" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="U12" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V12" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="W12" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" hidden="0">
       <x:c r="A13">
-        <x:v>12</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="2">
-        <x:v>45686.5269444444</x:v>
+        <x:v>45754.4636574074</x:v>
       </x:c>
       <x:c r="C13" s="2">
-        <x:v>45686.5275231481</x:v>
+        <x:v>45754.4790856481</x:v>
       </x:c>
       <x:c r="D13" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E13" s="10" t="s"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="10" t="s"/>
-      <x:c r="H13" s="10" t="s"/>
-      <x:c r="I13" s="7" t="s">
+      <x:c r="F13" s="10" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="J13" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K13" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
+      <x:c r="G13" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H13" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I13" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J13" s="10" t="s"/>
+      <x:c r="K13" s="10" t="s"/>
       <x:c r="L13" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="M13" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N13" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O13" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P13" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="Q13" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="R13" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="S13" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="T13" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="U13" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V13" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W13" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" hidden="0">
       <x:c r="A14">
-        <x:v>13</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B14" s="2">
-        <x:v>45686.5939814815</x:v>
+        <x:v>45754.4648842593</x:v>
       </x:c>
       <x:c r="C14" s="2">
-        <x:v>45686.6329050926</x:v>
+        <x:v>45754.4829398148</x:v>
       </x:c>
       <x:c r="D14" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E14" s="10" t="s"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="10" t="s"/>
-      <x:c r="H14" s="10" t="s"/>
-      <x:c r="I14" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="J14" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="K14" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
+      <x:c r="F14" s="10" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="G14" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H14" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I14" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J14" s="10" t="s"/>
+      <x:c r="K14" s="10" t="s"/>
       <x:c r="L14" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="M14" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N14" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O14" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="P14" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="R14" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="S14" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="T14" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="U14" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V14" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W14" s="7" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="15" hidden="0">
       <x:c r="A15">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="2">
-        <x:v>45686.832337963</x:v>
+        <x:v>45754.4964467593</x:v>
       </x:c>
       <x:c r="C15" s="2">
-        <x:v>45686.8411111111</x:v>
+        <x:v>45754.5039930556</x:v>
       </x:c>
       <x:c r="D15" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E15" s="10" t="s"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="10" t="s"/>
-      <x:c r="H15" s="10" t="s"/>
-      <x:c r="I15" s="7" t="s">
+      <x:c r="F15" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G15" s="10" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="J15" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K15" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
+      <x:c r="H15" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I15" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J15" s="10" t="s"/>
+      <x:c r="K15" s="10" t="s"/>
       <x:c r="L15" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="M15" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="N15" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="O15" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="P15" s="7" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="Q15" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="R15" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S15" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="T15" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U15" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="V15" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W15" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" hidden="0">
+      <x:c r="A16">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B16" s="2">
+        <x:v>45754.4942939815</x:v>
+      </x:c>
+      <x:c r="C16" s="2">
+        <x:v>45754.5079976852</x:v>
+      </x:c>
+      <x:c r="D16" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E16" s="10" t="s"/>
+      <x:c r="F16" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G16" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H16" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I16" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J16" s="10" t="s"/>
+      <x:c r="K16" s="10" t="s"/>
+      <x:c r="L16" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="M16" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="N16" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O16" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P16" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q16" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="R16" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S16" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="T16" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U16" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V16" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W16" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" hidden="0">
+      <x:c r="A17">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B17" s="2">
+        <x:v>45754.5269444444</x:v>
+      </x:c>
+      <x:c r="C17" s="2">
+        <x:v>45754.5305208333</x:v>
+      </x:c>
+      <x:c r="D17" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E17" s="10" t="s"/>
+      <x:c r="F17" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G17" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H17" s="10" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="I17" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J17" s="10" t="s"/>
+      <x:c r="K17" s="10" t="s"/>
+      <x:c r="L17" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M17" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N17" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="Q17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="R17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="S17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="T17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="U17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="V17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="W17" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" hidden="0">
+      <x:c r="A18">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B18" s="2">
+        <x:v>45754.5413657407</x:v>
+      </x:c>
+      <x:c r="C18" s="2">
+        <x:v>45754.5417939815</x:v>
+      </x:c>
+      <x:c r="D18" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E18" s="10" t="s"/>
+      <x:c r="F18" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G18" s="10" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="R15" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="S15" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="T15" s="7" t="s">
+      <x:c r="H18" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I18" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J18" s="10" t="s"/>
+      <x:c r="K18" s="10" t="s"/>
+      <x:c r="L18" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M18" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N18" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="O18" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P18" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q18" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="R18" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="S18" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T18" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U18" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="V18" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="W18" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" hidden="0">
+      <x:c r="A19">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B19" s="2">
+        <x:v>45754.5632986111</x:v>
+      </x:c>
+      <x:c r="C19" s="2">
+        <x:v>45754.5663888889</x:v>
+      </x:c>
+      <x:c r="D19" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E19" s="10" t="s"/>
+      <x:c r="F19" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G19" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H19" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I19" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J19" s="10" t="s"/>
+      <x:c r="K19" s="10" t="s"/>
+      <x:c r="L19" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M19" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N19" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O19" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="P19" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="Q19" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="R19" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S19" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="T19" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="U19" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="V19" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W19" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" hidden="0">
+      <x:c r="A20">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B20" s="2">
+        <x:v>45754.5449884259</x:v>
+      </x:c>
+      <x:c r="C20" s="2">
+        <x:v>45754.5806018518</x:v>
+      </x:c>
+      <x:c r="D20" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E20" s="10" t="s"/>
+      <x:c r="F20" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G20" s="10" t="s">
         <x:v>25</x:v>
+      </x:c>
+      <x:c r="H20" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I20" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J20" s="10" t="s"/>
+      <x:c r="K20" s="10" t="s"/>
+      <x:c r="L20" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M20" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N20" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O20" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P20" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q20" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R20" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S20" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T20" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U20" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V20" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W20" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" hidden="0">
+      <x:c r="A21">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B21" s="2">
+        <x:v>45754.6018402778</x:v>
+      </x:c>
+      <x:c r="C21" s="2">
+        <x:v>45754.6070717593</x:v>
+      </x:c>
+      <x:c r="D21" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E21" s="10" t="s"/>
+      <x:c r="F21" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G21" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H21" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I21" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J21" s="10" t="s"/>
+      <x:c r="K21" s="10" t="s"/>
+      <x:c r="L21" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="M21" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N21" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O21" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P21" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="Q21" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="R21" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="S21" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="T21" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U21" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="V21" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="W21" s="7" t="s">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rb5cc241ad1924afa"/>
+    <x:tablePart r:id="R898e2ea33d594f7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/analysis/app_responses.xlsx
+++ b/analysis/app_responses.xlsx
@@ -246,8 +246,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:W21" insertRow="1" totalsRowShown="0">
-  <x:autoFilter ref="A1:W21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:W25" insertRow="1" totalsRowShown="0">
+  <x:autoFilter ref="A1:W25"/>
   <x:tableColumns count="23">
     <x:tableColumn id="1" uniqueName="1" name="ID" dataDxfId="0"/>
     <x:tableColumn id="2" uniqueName="2" name="Start time" dataDxfId="3"/>
@@ -1973,11 +1973,271 @@
         <x:v>32</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" hidden="0">
+      <x:c r="A22">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B22" s="2">
+        <x:v>45755.4716087963</x:v>
+      </x:c>
+      <x:c r="C22" s="2">
+        <x:v>45755.476412037</x:v>
+      </x:c>
+      <x:c r="D22" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E22" s="10" t="s"/>
+      <x:c r="F22" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G22" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H22" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I22" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J22" s="10" t="s"/>
+      <x:c r="K22" s="10" t="s"/>
+      <x:c r="L22" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M22" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N22" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="O22" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="P22" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q22" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="R22" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S22" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T22" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U22" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V22" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W22" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" hidden="0">
+      <x:c r="A23">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B23" s="2">
+        <x:v>45755.4890740741</x:v>
+      </x:c>
+      <x:c r="C23" s="2">
+        <x:v>45755.4980902778</x:v>
+      </x:c>
+      <x:c r="D23" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E23" s="10" t="s"/>
+      <x:c r="F23" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G23" s="10" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="H23" s="10" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="I23" s="10" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="J23" s="10" t="s"/>
+      <x:c r="K23" s="10" t="s"/>
+      <x:c r="L23" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M23" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N23" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="O23" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P23" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q23" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="R23" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="S23" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T23" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U23" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="V23" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="W23" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" hidden="0">
+      <x:c r="A24">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B24" s="2">
+        <x:v>45755.5099768518</x:v>
+      </x:c>
+      <x:c r="C24" s="2">
+        <x:v>45755.5177314815</x:v>
+      </x:c>
+      <x:c r="D24" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E24" s="10" t="s"/>
+      <x:c r="F24" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G24" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H24" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="I24" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J24" s="10" t="s"/>
+      <x:c r="K24" s="10" t="s"/>
+      <x:c r="L24" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="M24" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="N24" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="O24" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="P24" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="Q24" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="R24" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="S24" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="T24" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="U24" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="V24" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="W24" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" hidden="0">
+      <x:c r="A25">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B25" s="2">
+        <x:v>45755.6278240741</x:v>
+      </x:c>
+      <x:c r="C25" s="2">
+        <x:v>45755.6300925926</x:v>
+      </x:c>
+      <x:c r="D25" s="10" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E25" s="10" t="s"/>
+      <x:c r="F25" s="10" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G25" s="10" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H25" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I25" s="10" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="J25" s="10" t="s"/>
+      <x:c r="K25" s="10" t="s"/>
+      <x:c r="L25" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="M25" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N25" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="O25" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="P25" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="Q25" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="R25" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="S25" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="T25" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="U25" s="7" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="V25" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="W25" s="7" t="s">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="R898e2ea33d594f7c"/>
+    <x:tablePart r:id="Rc0bdaf07949b4257"/>
   </x:tableParts>
 </x:worksheet>
 </file>